--- a/artfynd/S 1080-2025 artfynd.xlsx
+++ b/artfynd/S 1080-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AZ91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482472</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482476</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482561</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503641</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482478</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503631</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503633</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503634</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125615135</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1675,6 +1725,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125632426</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1778,6 +1833,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482535</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1875,6 +1935,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503636</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1972,6 +2037,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482568</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2073,6 +2143,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482692</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2170,6 +2245,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503665</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2271,6 +2351,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125619611</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2373,6 +2458,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482546</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2470,6 +2560,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482552</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2567,6 +2662,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482553</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2664,6 +2764,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482554</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2761,6 +2866,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482555</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2858,6 +2968,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482556</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2955,6 +3070,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482557</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3052,6 +3172,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482558</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3149,6 +3274,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482559</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3246,6 +3376,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503668</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3343,6 +3478,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503670</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3445,6 +3585,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528031</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3547,6 +3692,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528032</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3644,6 +3794,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528034</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3741,6 +3896,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528035</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3838,6 +3998,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528036</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3935,6 +4100,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528001</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4032,6 +4202,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482474</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4129,6 +4304,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125557857</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4226,6 +4406,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125557979</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4327,6 +4512,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125616322</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4433,6 +4623,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125616369</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4530,6 +4725,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482497</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4627,6 +4827,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482498</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4724,6 +4929,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482499</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4825,6 +5035,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482640</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4922,6 +5137,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503643</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5019,6 +5239,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503644</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5116,6 +5341,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134494046</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5213,6 +5443,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482484</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5315,6 +5550,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134527985</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5417,6 +5657,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482480</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5525,6 +5770,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125653603</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5633,6 +5883,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125616417</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5740,6 +5995,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125653324</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5837,6 +6097,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503684</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5934,6 +6199,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528048</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6031,6 +6301,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482560</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6128,6 +6403,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482493</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6225,6 +6505,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528025</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6322,6 +6607,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482501</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6419,6 +6709,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482500</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6516,6 +6811,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134527999</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6618,6 +6918,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125616287</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6724,6 +7029,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125619688</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6821,6 +7131,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125646895</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6918,6 +7233,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125646897</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7020,6 +7340,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482509</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7122,6 +7447,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482510</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7224,6 +7554,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482511</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7326,6 +7661,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482512</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7428,6 +7768,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482513</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7530,6 +7875,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482514</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7632,6 +7982,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482515</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7734,6 +8089,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482523</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7836,6 +8196,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482531</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7938,6 +8303,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482532</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8040,6 +8410,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482533</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8142,6 +8517,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482534</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8244,6 +8624,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482628</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8346,6 +8731,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482652</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8448,6 +8838,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482712</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8545,6 +8940,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503662</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8648,6 +9048,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528011</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8751,6 +9156,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134528012</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8848,6 +9258,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482536</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8945,6 +9360,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482537</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9042,6 +9462,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482487</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9139,6 +9564,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482488</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9236,6 +9666,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482489</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9333,6 +9768,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482490</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9430,6 +9870,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503637</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9527,6 +9972,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134503638</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9624,8 +10074,105 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134482503</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>